--- a/excels/CropConfig.xlsx
+++ b/excels/CropConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15345" windowHeight="25575"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
   <si>
     <t>唯一ID</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>作物</t>
     </r>
     <r>
@@ -124,34 +131,22 @@
     <t>[2,3]</t>
   </si>
   <si>
-    <t>烟草</t>
-  </si>
-  <si>
-    <t>高价值的经济作物。</t>
-  </si>
-  <si>
-    <t>仙人掌果</t>
-  </si>
-  <si>
-    <t>沙漠地带的特产。</t>
+    <t>小麦</t>
+  </si>
+  <si>
+    <t>广泛种植的基础粮食作物。</t>
+  </si>
+  <si>
+    <t>[1,3]</t>
+  </si>
+  <si>
+    <t>番茄</t>
+  </si>
+  <si>
+    <t>汁水丰富的番茄，可多次采摘。</t>
   </si>
   <si>
     <t>[2]</t>
-  </si>
-  <si>
-    <t>小麦</t>
-  </si>
-  <si>
-    <t>广泛种植的基础粮食作物。</t>
-  </si>
-  <si>
-    <t>[1,3]</t>
-  </si>
-  <si>
-    <t>番茄</t>
-  </si>
-  <si>
-    <t>汁水丰富的番茄，可多次采摘。</t>
   </si>
   <si>
     <t>土豆</t>
@@ -1180,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="20.625" defaultRowHeight="50" customHeight="1"/>
   <cols>
     <col min="1" max="16376" width="20.625" style="1" customWidth="1"/>
@@ -1344,22 +1339,22 @@
         <v>28</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:11">
@@ -1373,28 +1368,28 @@
         <v>103</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:11">
@@ -1408,13 +1403,13 @@
         <v>104</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G7" s="4">
         <v>3</v>
@@ -1422,11 +1417,11 @@
       <c r="H7" s="4">
         <v>3</v>
       </c>
-      <c r="I7" s="4">
-        <v>3</v>
-      </c>
-      <c r="J7" s="4">
-        <v>3</v>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
       </c>
       <c r="K7" s="4">
         <v>2</v>
@@ -1449,7 +1444,7 @@
         <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G8" s="4">
         <v>4</v>
@@ -1457,11 +1452,11 @@
       <c r="H8" s="4">
         <v>4</v>
       </c>
-      <c r="I8" s="4">
-        <v>4</v>
-      </c>
-      <c r="J8" s="4">
-        <v>3</v>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
       </c>
       <c r="K8" s="4">
         <v>3</v>
@@ -1484,13 +1479,13 @@
         <v>38</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G9" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
@@ -1499,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:11">
@@ -1513,13 +1508,13 @@
         <v>107</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G10" s="4">
         <v>4</v>
@@ -1527,14 +1522,14 @@
       <c r="H10" s="4">
         <v>4</v>
       </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
+      <c r="I10" s="4">
+        <v>4</v>
+      </c>
+      <c r="J10" s="4">
+        <v>2</v>
       </c>
       <c r="K10" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:11">
@@ -1548,19 +1543,19 @@
         <v>108</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="G11" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
@@ -1569,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:11">
@@ -1583,25 +1578,25 @@
         <v>109</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="4">
-        <v>4</v>
-      </c>
-      <c r="I12" s="4">
-        <v>4</v>
-      </c>
-      <c r="J12" s="4">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
       </c>
       <c r="K12" s="4">
         <v>2</v>
@@ -1618,13 +1613,13 @@
         <v>110</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G13" s="4">
         <v>5</v>
@@ -1632,83 +1627,13 @@
       <c r="H13" s="4">
         <v>5</v>
       </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2">
-        <v>0</v>
+      <c r="I13" s="4">
+        <v>5</v>
+      </c>
+      <c r="J13" s="4">
+        <v>5</v>
       </c>
       <c r="K13" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:11">
-      <c r="A14" s="4">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4">
-        <v>1011</v>
-      </c>
-      <c r="C14" s="4">
-        <v>111</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="4">
-        <v>3</v>
-      </c>
-      <c r="H14" s="4">
-        <v>3</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:11">
-      <c r="A15" s="4">
-        <v>12</v>
-      </c>
-      <c r="B15" s="4">
-        <v>1012</v>
-      </c>
-      <c r="C15" s="4">
-        <v>112</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="4">
-        <v>5</v>
-      </c>
-      <c r="H15" s="4">
-        <v>5</v>
-      </c>
-      <c r="I15" s="4">
-        <v>5</v>
-      </c>
-      <c r="J15" s="4">
-        <v>5</v>
-      </c>
-      <c r="K15" s="4">
         <v>3</v>
       </c>
     </row>
